--- a/Result/checksun_type/油電燃氣.xlsx
+++ b/Result/checksun_type/油電燃氣.xlsx
@@ -641,62 +641,62 @@
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>my_signal</t>
+          <t>up_up</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_3d</t>
+          <t>up_up_3d</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_5d</t>
+          <t>up_up_5d</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_10d</t>
+          <t>up_up_10d</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>up_up</t>
+          <t>bbw_cross</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>up_up_3d</t>
+          <t>MA_UP_d</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>up_up_5d</t>
+          <t>MA_UP_3d</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>up_up_10d</t>
+          <t>MA_UP_5d</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>bbw_cross</t>
+          <t>MA_UP_10d</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_3d</t>
+          <t>MA_UP_20d</t>
         </is>
       </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_5d</t>
+          <t>MA_UP_30d</t>
         </is>
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_10d</t>
+          <t>MA_UP_40d</t>
         </is>
       </c>
       <c r="BC1" s="1" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
@@ -1683,22 +1683,22 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
@@ -1893,11 +1893,15 @@
           <t>54.3</t>
         </is>
       </c>
-      <c r="CQ2" t="n">
-        <v>54.71</v>
-      </c>
-      <c r="CR2" t="n">
-        <v>55.03</v>
+      <c r="CQ2" t="inlineStr">
+        <is>
+          <t>54.71</t>
+        </is>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>55.03</t>
+        </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
@@ -2650,7 +2654,7 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -2665,22 +2669,22 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
@@ -2875,11 +2879,15 @@
           <t>54.29</t>
         </is>
       </c>
-      <c r="CQ3" t="n">
-        <v>54.75</v>
-      </c>
-      <c r="CR3" t="n">
-        <v>55.05</v>
+      <c r="CQ3" t="inlineStr">
+        <is>
+          <t>54.75</t>
+        </is>
+      </c>
+      <c r="CR3" t="inlineStr">
+        <is>
+          <t>55.05</t>
+        </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
@@ -3632,7 +3640,7 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
@@ -3647,22 +3655,22 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
@@ -3857,11 +3865,15 @@
           <t>54.32000000000001</t>
         </is>
       </c>
-      <c r="CQ4" t="n">
-        <v>54.78</v>
-      </c>
-      <c r="CR4" t="n">
-        <v>55.08</v>
+      <c r="CQ4" t="inlineStr">
+        <is>
+          <t>54.78</t>
+        </is>
+      </c>
+      <c r="CR4" t="inlineStr">
+        <is>
+          <t>55.08</t>
+        </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
@@ -4614,7 +4626,7 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
@@ -4629,22 +4641,22 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
@@ -4839,11 +4851,15 @@
           <t>54.35</t>
         </is>
       </c>
-      <c r="CQ5" t="n">
-        <v>54.8</v>
-      </c>
-      <c r="CR5" t="n">
-        <v>55.1</v>
+      <c r="CQ5" t="inlineStr">
+        <is>
+          <t>54.8</t>
+        </is>
+      </c>
+      <c r="CR5" t="inlineStr">
+        <is>
+          <t>55.1</t>
+        </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
@@ -5596,7 +5612,7 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
@@ -5611,22 +5627,22 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -5821,11 +5837,15 @@
           <t>54.44</t>
         </is>
       </c>
-      <c r="CQ6" t="n">
-        <v>54.86</v>
-      </c>
-      <c r="CR6" t="n">
-        <v>55.12</v>
+      <c r="CQ6" t="inlineStr">
+        <is>
+          <t>54.86</t>
+        </is>
+      </c>
+      <c r="CR6" t="inlineStr">
+        <is>
+          <t>55.12</t>
+        </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
@@ -6578,7 +6598,7 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
@@ -6593,22 +6613,22 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
@@ -6803,11 +6823,15 @@
           <t>54.58</t>
         </is>
       </c>
-      <c r="CQ7" t="n">
-        <v>54.9</v>
-      </c>
-      <c r="CR7" t="n">
-        <v>55.14</v>
+      <c r="CQ7" t="inlineStr">
+        <is>
+          <t>54.9</t>
+        </is>
+      </c>
+      <c r="CR7" t="inlineStr">
+        <is>
+          <t>55.14</t>
+        </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
@@ -7560,7 +7584,7 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
@@ -7575,22 +7599,22 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
@@ -7785,11 +7809,15 @@
           <t>54.73</t>
         </is>
       </c>
-      <c r="CQ8" t="n">
-        <v>54.96</v>
-      </c>
-      <c r="CR8" t="n">
-        <v>55.2</v>
+      <c r="CQ8" t="inlineStr">
+        <is>
+          <t>54.96</t>
+        </is>
+      </c>
+      <c r="CR8" t="inlineStr">
+        <is>
+          <t>55.2</t>
+        </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
@@ -8542,7 +8570,7 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
@@ -8557,22 +8585,22 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -8767,11 +8795,15 @@
           <t>54.83000000000001</t>
         </is>
       </c>
-      <c r="CQ9" t="n">
-        <v>55</v>
-      </c>
-      <c r="CR9" t="n">
-        <v>55.24</v>
+      <c r="CQ9" t="inlineStr">
+        <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="CR9" t="inlineStr">
+        <is>
+          <t>55.24</t>
+        </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
@@ -9524,7 +9556,7 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
@@ -9539,22 +9571,22 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
@@ -9749,11 +9781,15 @@
           <t>54.98</t>
         </is>
       </c>
-      <c r="CQ10" t="n">
-        <v>55.04</v>
-      </c>
-      <c r="CR10" t="n">
-        <v>55.27</v>
+      <c r="CQ10" t="inlineStr">
+        <is>
+          <t>55.04</t>
+        </is>
+      </c>
+      <c r="CR10" t="inlineStr">
+        <is>
+          <t>55.27</t>
+        </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
@@ -10506,7 +10542,7 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
@@ -10521,22 +10557,22 @@
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
@@ -10731,11 +10767,15 @@
           <t>33.975</t>
         </is>
       </c>
-      <c r="CQ11" t="n">
-        <v>34.01</v>
-      </c>
-      <c r="CR11" t="n">
-        <v>33.94</v>
+      <c r="CQ11" t="inlineStr">
+        <is>
+          <t>34.01</t>
+        </is>
+      </c>
+      <c r="CR11" t="inlineStr">
+        <is>
+          <t>33.94</t>
+        </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
@@ -11488,7 +11528,7 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
@@ -11503,22 +11543,22 @@
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
@@ -11713,11 +11753,15 @@
           <t>33.985</t>
         </is>
       </c>
-      <c r="CQ12" t="n">
-        <v>34.02</v>
-      </c>
-      <c r="CR12" t="n">
-        <v>33.94</v>
+      <c r="CQ12" t="inlineStr">
+        <is>
+          <t>34.02</t>
+        </is>
+      </c>
+      <c r="CR12" t="inlineStr">
+        <is>
+          <t>33.94</t>
+        </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
@@ -12470,7 +12514,7 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
@@ -12485,22 +12529,22 @@
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
@@ -12695,11 +12739,15 @@
           <t>33.965</t>
         </is>
       </c>
-      <c r="CQ13" t="n">
-        <v>34.01</v>
-      </c>
-      <c r="CR13" t="n">
-        <v>33.93</v>
+      <c r="CQ13" t="inlineStr">
+        <is>
+          <t>34.01</t>
+        </is>
+      </c>
+      <c r="CR13" t="inlineStr">
+        <is>
+          <t>33.93</t>
+        </is>
       </c>
       <c r="CS13" t="inlineStr">
         <is>
@@ -13452,7 +13500,7 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
@@ -13467,22 +13515,22 @@
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
@@ -13677,11 +13725,15 @@
           <t>33.935</t>
         </is>
       </c>
-      <c r="CQ14" t="n">
-        <v>33.99</v>
-      </c>
-      <c r="CR14" t="n">
-        <v>33.93</v>
+      <c r="CQ14" t="inlineStr">
+        <is>
+          <t>33.99</t>
+        </is>
+      </c>
+      <c r="CR14" t="inlineStr">
+        <is>
+          <t>33.93</t>
+        </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
@@ -14434,7 +14486,7 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
@@ -14449,22 +14501,22 @@
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
@@ -14659,11 +14711,15 @@
           <t>33.985</t>
         </is>
       </c>
-      <c r="CQ15" t="n">
-        <v>34</v>
-      </c>
-      <c r="CR15" t="n">
-        <v>33.93</v>
+      <c r="CQ15" t="inlineStr">
+        <is>
+          <t>34.0</t>
+        </is>
+      </c>
+      <c r="CR15" t="inlineStr">
+        <is>
+          <t>33.93</t>
+        </is>
       </c>
       <c r="CS15" t="inlineStr">
         <is>
@@ -15416,7 +15472,7 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
@@ -15431,22 +15487,22 @@
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
@@ -15641,11 +15697,15 @@
           <t>34.02</t>
         </is>
       </c>
-      <c r="CQ16" t="n">
-        <v>34.01</v>
-      </c>
-      <c r="CR16" t="n">
-        <v>33.93</v>
+      <c r="CQ16" t="inlineStr">
+        <is>
+          <t>34.01</t>
+        </is>
+      </c>
+      <c r="CR16" t="inlineStr">
+        <is>
+          <t>33.93</t>
+        </is>
       </c>
       <c r="CS16" t="inlineStr">
         <is>
@@ -16398,7 +16458,7 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
@@ -16413,22 +16473,22 @@
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
@@ -16623,11 +16683,15 @@
           <t>34.05</t>
         </is>
       </c>
-      <c r="CQ17" t="n">
-        <v>34.03</v>
-      </c>
-      <c r="CR17" t="n">
-        <v>33.93</v>
+      <c r="CQ17" t="inlineStr">
+        <is>
+          <t>34.03</t>
+        </is>
+      </c>
+      <c r="CR17" t="inlineStr">
+        <is>
+          <t>33.93</t>
+        </is>
       </c>
       <c r="CS17" t="inlineStr">
         <is>
@@ -17380,7 +17444,7 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
@@ -17395,22 +17459,22 @@
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
@@ -17605,11 +17669,15 @@
           <t>34.065</t>
         </is>
       </c>
-      <c r="CQ18" t="n">
-        <v>34.03</v>
-      </c>
-      <c r="CR18" t="n">
-        <v>33.92</v>
+      <c r="CQ18" t="inlineStr">
+        <is>
+          <t>34.03</t>
+        </is>
+      </c>
+      <c r="CR18" t="inlineStr">
+        <is>
+          <t>33.92</t>
+        </is>
       </c>
       <c r="CS18" t="inlineStr">
         <is>
@@ -18362,7 +18430,7 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
@@ -18377,22 +18445,22 @@
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
@@ -18587,11 +18655,15 @@
           <t>34.08</t>
         </is>
       </c>
-      <c r="CQ19" t="n">
-        <v>34.03</v>
-      </c>
-      <c r="CR19" t="n">
-        <v>33.9</v>
+      <c r="CQ19" t="inlineStr">
+        <is>
+          <t>34.03</t>
+        </is>
+      </c>
+      <c r="CR19" t="inlineStr">
+        <is>
+          <t>33.9</t>
+        </is>
       </c>
       <c r="CS19" t="inlineStr">
         <is>
@@ -19344,7 +19416,7 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
@@ -19359,22 +19431,22 @@
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
@@ -19569,11 +19641,15 @@
           <t>49.11499999999999</t>
         </is>
       </c>
-      <c r="CQ20" t="n">
-        <v>49.22</v>
-      </c>
-      <c r="CR20" t="n">
-        <v>49.21</v>
+      <c r="CQ20" t="inlineStr">
+        <is>
+          <t>49.22</t>
+        </is>
+      </c>
+      <c r="CR20" t="inlineStr">
+        <is>
+          <t>49.21</t>
+        </is>
       </c>
       <c r="CS20" t="inlineStr">
         <is>
@@ -20089,11 +20165,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>【c】</t>
-        </is>
-      </c>
+      <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
           <t>9926</t>
@@ -20326,7 +20398,7 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
@@ -20341,22 +20413,22 @@
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
@@ -20551,11 +20623,15 @@
           <t>49.14</t>
         </is>
       </c>
-      <c r="CQ21" t="n">
-        <v>49.22</v>
-      </c>
-      <c r="CR21" t="n">
-        <v>49.22</v>
+      <c r="CQ21" t="inlineStr">
+        <is>
+          <t>49.22</t>
+        </is>
+      </c>
+      <c r="CR21" t="inlineStr">
+        <is>
+          <t>49.22</t>
+        </is>
       </c>
       <c r="CS21" t="inlineStr">
         <is>
@@ -21308,7 +21384,7 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
@@ -21318,27 +21394,27 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
@@ -21533,11 +21609,15 @@
           <t>49.13</t>
         </is>
       </c>
-      <c r="CQ22" t="n">
-        <v>49.2</v>
-      </c>
-      <c r="CR22" t="n">
-        <v>49.22</v>
+      <c r="CQ22" t="inlineStr">
+        <is>
+          <t>49.2</t>
+        </is>
+      </c>
+      <c r="CR22" t="inlineStr">
+        <is>
+          <t>49.22</t>
+        </is>
       </c>
       <c r="CS22" t="inlineStr">
         <is>
@@ -22290,7 +22370,7 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
@@ -22300,27 +22380,27 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
@@ -22515,11 +22595,15 @@
           <t>49.17</t>
         </is>
       </c>
-      <c r="CQ23" t="n">
-        <v>49.19</v>
-      </c>
-      <c r="CR23" t="n">
-        <v>49.26</v>
+      <c r="CQ23" t="inlineStr">
+        <is>
+          <t>49.19</t>
+        </is>
+      </c>
+      <c r="CR23" t="inlineStr">
+        <is>
+          <t>49.26</t>
+        </is>
       </c>
       <c r="CS23" t="inlineStr">
         <is>
@@ -23272,37 +23356,37 @@
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
@@ -23497,11 +23581,15 @@
           <t>49.23</t>
         </is>
       </c>
-      <c r="CQ24" t="n">
-        <v>49.2</v>
-      </c>
-      <c r="CR24" t="n">
-        <v>49.3</v>
+      <c r="CQ24" t="inlineStr">
+        <is>
+          <t>49.2</t>
+        </is>
+      </c>
+      <c r="CR24" t="inlineStr">
+        <is>
+          <t>49.3</t>
+        </is>
       </c>
       <c r="CS24" t="inlineStr">
         <is>
@@ -24254,37 +24342,37 @@
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
@@ -24479,11 +24567,15 @@
           <t>49.285</t>
         </is>
       </c>
-      <c r="CQ25" t="n">
-        <v>49.2</v>
-      </c>
-      <c r="CR25" t="n">
-        <v>49.32</v>
+      <c r="CQ25" t="inlineStr">
+        <is>
+          <t>49.2</t>
+        </is>
+      </c>
+      <c r="CR25" t="inlineStr">
+        <is>
+          <t>49.32</t>
+        </is>
       </c>
       <c r="CS25" t="inlineStr">
         <is>
@@ -25236,37 +25328,37 @@
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
@@ -25461,11 +25553,15 @@
           <t>49.3</t>
         </is>
       </c>
-      <c r="CQ26" t="n">
-        <v>49.24</v>
-      </c>
-      <c r="CR26" t="n">
-        <v>49.34</v>
+      <c r="CQ26" t="inlineStr">
+        <is>
+          <t>49.24</t>
+        </is>
+      </c>
+      <c r="CR26" t="inlineStr">
+        <is>
+          <t>49.34</t>
+        </is>
       </c>
       <c r="CS26" t="inlineStr">
         <is>
@@ -26218,7 +26314,7 @@
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
@@ -26233,22 +26329,22 @@
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
@@ -26443,11 +26539,15 @@
           <t>49.32000000000001</t>
         </is>
       </c>
-      <c r="CQ27" t="n">
-        <v>49.22</v>
-      </c>
-      <c r="CR27" t="n">
-        <v>49.35</v>
+      <c r="CQ27" t="inlineStr">
+        <is>
+          <t>49.22</t>
+        </is>
+      </c>
+      <c r="CR27" t="inlineStr">
+        <is>
+          <t>49.35</t>
+        </is>
       </c>
       <c r="CS27" t="inlineStr">
         <is>
@@ -27200,7 +27300,7 @@
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
@@ -27215,17 +27315,17 @@
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
@@ -27425,11 +27525,15 @@
           <t>49.34</t>
         </is>
       </c>
-      <c r="CQ28" t="n">
-        <v>49.21</v>
-      </c>
-      <c r="CR28" t="n">
-        <v>49.36</v>
+      <c r="CQ28" t="inlineStr">
+        <is>
+          <t>49.21</t>
+        </is>
+      </c>
+      <c r="CR28" t="inlineStr">
+        <is>
+          <t>49.36</t>
+        </is>
       </c>
       <c r="CS28" t="inlineStr">
         <is>
@@ -28182,7 +28286,7 @@
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
@@ -28197,22 +28301,22 @@
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
@@ -28407,11 +28511,15 @@
           <t>43.0</t>
         </is>
       </c>
-      <c r="CQ29" t="n">
-        <v>43.11</v>
-      </c>
-      <c r="CR29" t="n">
-        <v>42.95</v>
+      <c r="CQ29" t="inlineStr">
+        <is>
+          <t>43.11</t>
+        </is>
+      </c>
+      <c r="CR29" t="inlineStr">
+        <is>
+          <t>42.95</t>
+        </is>
       </c>
       <c r="CS29" t="inlineStr">
         <is>
@@ -29164,7 +29272,7 @@
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
@@ -29179,22 +29287,22 @@
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
@@ -29389,11 +29497,15 @@
           <t>42.97</t>
         </is>
       </c>
-      <c r="CQ30" t="n">
-        <v>43.09</v>
-      </c>
-      <c r="CR30" t="n">
-        <v>42.96</v>
+      <c r="CQ30" t="inlineStr">
+        <is>
+          <t>43.09</t>
+        </is>
+      </c>
+      <c r="CR30" t="inlineStr">
+        <is>
+          <t>42.96</t>
+        </is>
       </c>
       <c r="CS30" t="inlineStr">
         <is>
@@ -30146,7 +30258,7 @@
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
@@ -30161,22 +30273,22 @@
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
@@ -30371,11 +30483,15 @@
           <t>42.93</t>
         </is>
       </c>
-      <c r="CQ31" t="n">
-        <v>43.08</v>
-      </c>
-      <c r="CR31" t="n">
-        <v>42.97</v>
+      <c r="CQ31" t="inlineStr">
+        <is>
+          <t>43.08</t>
+        </is>
+      </c>
+      <c r="CR31" t="inlineStr">
+        <is>
+          <t>42.97</t>
+        </is>
       </c>
       <c r="CS31" t="inlineStr">
         <is>
@@ -31128,7 +31244,7 @@
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
@@ -31143,22 +31259,22 @@
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
@@ -31353,11 +31469,15 @@
           <t>42.965</t>
         </is>
       </c>
-      <c r="CQ32" t="n">
-        <v>43.06</v>
-      </c>
-      <c r="CR32" t="n">
-        <v>42.98</v>
+      <c r="CQ32" t="inlineStr">
+        <is>
+          <t>43.06</t>
+        </is>
+      </c>
+      <c r="CR32" t="inlineStr">
+        <is>
+          <t>42.98</t>
+        </is>
       </c>
       <c r="CS32" t="inlineStr">
         <is>
@@ -32110,7 +32230,7 @@
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
@@ -32125,22 +32245,22 @@
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
@@ -32335,11 +32455,15 @@
           <t>43.035</t>
         </is>
       </c>
-      <c r="CQ33" t="n">
-        <v>43.08</v>
-      </c>
-      <c r="CR33" t="n">
-        <v>43.02</v>
+      <c r="CQ33" t="inlineStr">
+        <is>
+          <t>43.08</t>
+        </is>
+      </c>
+      <c r="CR33" t="inlineStr">
+        <is>
+          <t>43.02</t>
+        </is>
       </c>
       <c r="CS33" t="inlineStr">
         <is>
@@ -33092,7 +33216,7 @@
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
@@ -33107,22 +33231,22 @@
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
@@ -33317,11 +33441,15 @@
           <t>43.11499999999999</t>
         </is>
       </c>
-      <c r="CQ34" t="n">
-        <v>43.08</v>
-      </c>
-      <c r="CR34" t="n">
-        <v>43.04</v>
+      <c r="CQ34" t="inlineStr">
+        <is>
+          <t>43.08</t>
+        </is>
+      </c>
+      <c r="CR34" t="inlineStr">
+        <is>
+          <t>43.04</t>
+        </is>
       </c>
       <c r="CS34" t="inlineStr">
         <is>
@@ -34074,7 +34202,7 @@
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
@@ -34089,22 +34217,22 @@
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
@@ -34299,11 +34427,15 @@
           <t>43.185</t>
         </is>
       </c>
-      <c r="CQ35" t="n">
-        <v>43.11</v>
-      </c>
-      <c r="CR35" t="n">
-        <v>43.07</v>
+      <c r="CQ35" t="inlineStr">
+        <is>
+          <t>43.11</t>
+        </is>
+      </c>
+      <c r="CR35" t="inlineStr">
+        <is>
+          <t>43.07</t>
+        </is>
       </c>
       <c r="CS35" t="inlineStr">
         <is>
@@ -34819,11 +34951,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>【c】</t>
-        </is>
-      </c>
+      <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
           <t>9918</t>
@@ -35056,7 +35184,7 @@
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
@@ -35071,22 +35199,22 @@
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC36" t="inlineStr">
@@ -35281,11 +35409,15 @@
           <t>43.205</t>
         </is>
       </c>
-      <c r="CQ36" t="n">
-        <v>43.09</v>
-      </c>
-      <c r="CR36" t="n">
-        <v>43.09</v>
+      <c r="CQ36" t="inlineStr">
+        <is>
+          <t>43.09</t>
+        </is>
+      </c>
+      <c r="CR36" t="inlineStr">
+        <is>
+          <t>43.09</t>
+        </is>
       </c>
       <c r="CS36" t="inlineStr">
         <is>
@@ -36038,7 +36170,7 @@
       </c>
       <c r="AV37" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW37" t="inlineStr">
@@ -36048,27 +36180,27 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB37" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC37" t="inlineStr">
@@ -36263,11 +36395,15 @@
           <t>43.21</t>
         </is>
       </c>
-      <c r="CQ37" t="n">
-        <v>43.1</v>
-      </c>
-      <c r="CR37" t="n">
-        <v>43.1</v>
+      <c r="CQ37" t="inlineStr">
+        <is>
+          <t>43.1</t>
+        </is>
+      </c>
+      <c r="CR37" t="inlineStr">
+        <is>
+          <t>43.1</t>
+        </is>
       </c>
       <c r="CS37" t="inlineStr">
         <is>
@@ -37020,7 +37156,7 @@
       </c>
       <c r="AV38" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW38" t="inlineStr">
@@ -37035,22 +37171,22 @@
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BB38" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BC38" t="inlineStr">
@@ -37245,11 +37381,15 @@
           <t>28.98</t>
         </is>
       </c>
-      <c r="CQ38" t="n">
-        <v>29.01</v>
-      </c>
-      <c r="CR38" t="n">
-        <v>29.08</v>
+      <c r="CQ38" t="inlineStr">
+        <is>
+          <t>29.01</t>
+        </is>
+      </c>
+      <c r="CR38" t="inlineStr">
+        <is>
+          <t>29.08</t>
+        </is>
       </c>
       <c r="CS38" t="inlineStr">
         <is>
@@ -38002,7 +38142,7 @@
       </c>
       <c r="AV39" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW39" t="inlineStr">
@@ -38017,22 +38157,22 @@
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BB39" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BC39" t="inlineStr">
@@ -38227,11 +38367,15 @@
           <t>28.985</t>
         </is>
       </c>
-      <c r="CQ39" t="n">
-        <v>29.01</v>
-      </c>
-      <c r="CR39" t="n">
-        <v>29.08</v>
+      <c r="CQ39" t="inlineStr">
+        <is>
+          <t>29.01</t>
+        </is>
+      </c>
+      <c r="CR39" t="inlineStr">
+        <is>
+          <t>29.08</t>
+        </is>
       </c>
       <c r="CS39" t="inlineStr">
         <is>
@@ -38984,7 +39128,7 @@
       </c>
       <c r="AV40" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW40" t="inlineStr">
@@ -38999,22 +39143,22 @@
       </c>
       <c r="AY40" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BB40" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BC40" t="inlineStr">
@@ -39209,11 +39353,15 @@
           <t>28.99</t>
         </is>
       </c>
-      <c r="CQ40" t="n">
-        <v>29.02</v>
-      </c>
-      <c r="CR40" t="n">
-        <v>29.08</v>
+      <c r="CQ40" t="inlineStr">
+        <is>
+          <t>29.02</t>
+        </is>
+      </c>
+      <c r="CR40" t="inlineStr">
+        <is>
+          <t>29.08</t>
+        </is>
       </c>
       <c r="CS40" t="inlineStr">
         <is>
@@ -39966,7 +40114,7 @@
       </c>
       <c r="AV41" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW41" t="inlineStr">
@@ -39981,22 +40129,22 @@
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BB41" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BC41" t="inlineStr">
@@ -40191,11 +40339,15 @@
           <t>28.985</t>
         </is>
       </c>
-      <c r="CQ41" t="n">
-        <v>29.02</v>
-      </c>
-      <c r="CR41" t="n">
-        <v>29.09</v>
+      <c r="CQ41" t="inlineStr">
+        <is>
+          <t>29.02</t>
+        </is>
+      </c>
+      <c r="CR41" t="inlineStr">
+        <is>
+          <t>29.09</t>
+        </is>
       </c>
       <c r="CS41" t="inlineStr">
         <is>
@@ -40948,7 +41100,7 @@
       </c>
       <c r="AV42" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW42" t="inlineStr">
@@ -40963,22 +41115,22 @@
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BB42" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BC42" t="inlineStr">
@@ -41173,11 +41325,15 @@
           <t>28.99</t>
         </is>
       </c>
-      <c r="CQ42" t="n">
-        <v>29.02</v>
-      </c>
-      <c r="CR42" t="n">
-        <v>29.09</v>
+      <c r="CQ42" t="inlineStr">
+        <is>
+          <t>29.02</t>
+        </is>
+      </c>
+      <c r="CR42" t="inlineStr">
+        <is>
+          <t>29.09</t>
+        </is>
       </c>
       <c r="CS42" t="inlineStr">
         <is>
@@ -41930,7 +42086,7 @@
       </c>
       <c r="AV43" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW43" t="inlineStr">
@@ -41945,22 +42101,22 @@
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BB43" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BC43" t="inlineStr">
@@ -42155,11 +42311,15 @@
           <t>29.0</t>
         </is>
       </c>
-      <c r="CQ43" t="n">
-        <v>29.02</v>
-      </c>
-      <c r="CR43" t="n">
-        <v>29.1</v>
+      <c r="CQ43" t="inlineStr">
+        <is>
+          <t>29.02</t>
+        </is>
+      </c>
+      <c r="CR43" t="inlineStr">
+        <is>
+          <t>29.1</t>
+        </is>
       </c>
       <c r="CS43" t="inlineStr">
         <is>
@@ -42912,7 +43072,7 @@
       </c>
       <c r="AV44" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW44" t="inlineStr">
@@ -42927,22 +43087,22 @@
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BB44" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BC44" t="inlineStr">
@@ -43137,11 +43297,15 @@
           <t>29.01</t>
         </is>
       </c>
-      <c r="CQ44" t="n">
-        <v>29.04</v>
-      </c>
-      <c r="CR44" t="n">
-        <v>29.1</v>
+      <c r="CQ44" t="inlineStr">
+        <is>
+          <t>29.04</t>
+        </is>
+      </c>
+      <c r="CR44" t="inlineStr">
+        <is>
+          <t>29.1</t>
+        </is>
       </c>
       <c r="CS44" t="inlineStr">
         <is>
@@ -43894,7 +44058,7 @@
       </c>
       <c r="AV45" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW45" t="inlineStr">
@@ -43909,17 +44073,17 @@
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BB45" t="inlineStr">
@@ -44119,11 +44283,15 @@
           <t>29.02</t>
         </is>
       </c>
-      <c r="CQ45" t="n">
-        <v>29.04</v>
-      </c>
-      <c r="CR45" t="n">
-        <v>29.12</v>
+      <c r="CQ45" t="inlineStr">
+        <is>
+          <t>29.04</t>
+        </is>
+      </c>
+      <c r="CR45" t="inlineStr">
+        <is>
+          <t>29.12</t>
+        </is>
       </c>
       <c r="CS45" t="inlineStr">
         <is>
@@ -44876,7 +45044,7 @@
       </c>
       <c r="AV46" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW46" t="inlineStr">
@@ -44891,17 +45059,17 @@
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BB46" t="inlineStr">
@@ -45101,11 +45269,15 @@
           <t>29.035</t>
         </is>
       </c>
-      <c r="CQ46" t="n">
-        <v>29.04</v>
-      </c>
-      <c r="CR46" t="n">
-        <v>29.13</v>
+      <c r="CQ46" t="inlineStr">
+        <is>
+          <t>29.04</t>
+        </is>
+      </c>
+      <c r="CR46" t="inlineStr">
+        <is>
+          <t>29.13</t>
+        </is>
       </c>
       <c r="CS46" t="inlineStr">
         <is>
@@ -45843,52 +46015,52 @@
       </c>
       <c r="AS47" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AV47" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW47" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AT47" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-      <c r="AU47" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV47" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW47" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BB47" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC47" t="inlineStr">
@@ -46083,11 +46255,15 @@
           <t>43.06</t>
         </is>
       </c>
-      <c r="CQ47" t="n">
-        <v>42.35</v>
-      </c>
-      <c r="CR47" t="n">
-        <v>41.62</v>
+      <c r="CQ47" t="inlineStr">
+        <is>
+          <t>42.35</t>
+        </is>
+      </c>
+      <c r="CR47" t="inlineStr">
+        <is>
+          <t>41.62</t>
+        </is>
       </c>
       <c r="CS47" t="inlineStr">
         <is>
@@ -46825,52 +47001,52 @@
       </c>
       <c r="AS48" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AV48" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW48" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AT48" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-      <c r="AU48" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV48" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW48" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BB48" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC48" t="inlineStr">
@@ -47065,11 +47241,15 @@
           <t>43.075</t>
         </is>
       </c>
-      <c r="CQ48" t="n">
-        <v>42.27</v>
-      </c>
-      <c r="CR48" t="n">
-        <v>41.6</v>
+      <c r="CQ48" t="inlineStr">
+        <is>
+          <t>42.27</t>
+        </is>
+      </c>
+      <c r="CR48" t="inlineStr">
+        <is>
+          <t>41.6</t>
+        </is>
       </c>
       <c r="CS48" t="inlineStr">
         <is>
@@ -47802,57 +47982,57 @@
       </c>
       <c r="AR49" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS49" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AS49" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AT49" t="inlineStr">
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AV49" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
         <is>
           <t>6.0</t>
         </is>
       </c>
-      <c r="AU49" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV49" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW49" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BB49" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC49" t="inlineStr">
@@ -48047,11 +48227,15 @@
           <t>43.12</t>
         </is>
       </c>
-      <c r="CQ49" t="n">
-        <v>42.21</v>
-      </c>
-      <c r="CR49" t="n">
-        <v>41.58</v>
+      <c r="CQ49" t="inlineStr">
+        <is>
+          <t>42.21</t>
+        </is>
+      </c>
+      <c r="CR49" t="inlineStr">
+        <is>
+          <t>41.58</t>
+        </is>
       </c>
       <c r="CS49" t="inlineStr">
         <is>
@@ -48784,57 +48968,57 @@
       </c>
       <c r="AR50" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS50" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AS50" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AT50" t="inlineStr">
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AV50" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
         <is>
           <t>6.0</t>
         </is>
       </c>
-      <c r="AU50" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV50" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW50" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BB50" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BC50" t="inlineStr">
@@ -49029,11 +49213,15 @@
           <t>43.115</t>
         </is>
       </c>
-      <c r="CQ50" t="n">
-        <v>42.11</v>
-      </c>
-      <c r="CR50" t="n">
-        <v>41.54</v>
+      <c r="CQ50" t="inlineStr">
+        <is>
+          <t>42.11</t>
+        </is>
+      </c>
+      <c r="CR50" t="inlineStr">
+        <is>
+          <t>41.54</t>
+        </is>
       </c>
       <c r="CS50" t="inlineStr">
         <is>
@@ -49761,62 +49949,62 @@
       </c>
       <c r="AQ51" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS51" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR51" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AS51" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="AT51" t="inlineStr">
+      <c r="AV51" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
         <is>
           <t>6.0</t>
         </is>
       </c>
-      <c r="AU51" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV51" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW51" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB51" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC51" t="inlineStr">
@@ -50011,11 +50199,15 @@
           <t>42.925</t>
         </is>
       </c>
-      <c r="CQ51" t="n">
-        <v>42.01</v>
-      </c>
-      <c r="CR51" t="n">
-        <v>41.5</v>
+      <c r="CQ51" t="inlineStr">
+        <is>
+          <t>42.01</t>
+        </is>
+      </c>
+      <c r="CR51" t="inlineStr">
+        <is>
+          <t>41.5</t>
+        </is>
       </c>
       <c r="CS51" t="inlineStr">
         <is>
@@ -50743,32 +50935,32 @@
       </c>
       <c r="AQ52" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR52" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS52" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR52" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AS52" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="AT52" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="AU52" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AV52" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW52" t="inlineStr">
@@ -50783,22 +50975,22 @@
       </c>
       <c r="AY52" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB52" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC52" t="inlineStr">
@@ -50993,11 +51185,15 @@
           <t>42.725</t>
         </is>
       </c>
-      <c r="CQ52" t="n">
-        <v>41.92</v>
-      </c>
-      <c r="CR52" t="n">
-        <v>41.49</v>
+      <c r="CQ52" t="inlineStr">
+        <is>
+          <t>41.92</t>
+        </is>
+      </c>
+      <c r="CR52" t="inlineStr">
+        <is>
+          <t>41.49</t>
+        </is>
       </c>
       <c r="CS52" t="inlineStr">
         <is>
@@ -51725,62 +51921,62 @@
       </c>
       <c r="AQ53" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS53" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR53" t="inlineStr">
+      <c r="AV53" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AS53" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AT53" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AU53" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV53" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW53" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
       <c r="AY53" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB53" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC53" t="inlineStr">
@@ -51975,11 +52171,15 @@
           <t>42.52</t>
         </is>
       </c>
-      <c r="CQ53" t="n">
-        <v>41.82</v>
-      </c>
-      <c r="CR53" t="n">
-        <v>41.48</v>
+      <c r="CQ53" t="inlineStr">
+        <is>
+          <t>41.82</t>
+        </is>
+      </c>
+      <c r="CR53" t="inlineStr">
+        <is>
+          <t>41.48</t>
+        </is>
       </c>
       <c r="CS53" t="inlineStr">
         <is>
@@ -52707,62 +52907,62 @@
       </c>
       <c r="AQ54" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR54" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS54" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AT54" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR54" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AS54" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AT54" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AU54" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AV54" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC54" t="inlineStr">
@@ -52957,11 +53157,15 @@
           <t>42.305</t>
         </is>
       </c>
-      <c r="CQ54" t="n">
-        <v>41.71</v>
-      </c>
-      <c r="CR54" t="n">
-        <v>41.46</v>
+      <c r="CQ54" t="inlineStr">
+        <is>
+          <t>41.71</t>
+        </is>
+      </c>
+      <c r="CR54" t="inlineStr">
+        <is>
+          <t>41.46</t>
+        </is>
       </c>
       <c r="CS54" t="inlineStr">
         <is>
@@ -53689,62 +53893,62 @@
       </c>
       <c r="AQ55" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR55" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS55" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AT55" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR55" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AS55" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AT55" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AU55" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AV55" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC55" t="inlineStr">
@@ -53939,11 +54143,15 @@
           <t>42.11</t>
         </is>
       </c>
-      <c r="CQ55" t="n">
-        <v>41.61</v>
-      </c>
-      <c r="CR55" t="n">
-        <v>41.45</v>
+      <c r="CQ55" t="inlineStr">
+        <is>
+          <t>41.61</t>
+        </is>
+      </c>
+      <c r="CR55" t="inlineStr">
+        <is>
+          <t>41.45</t>
+        </is>
       </c>
       <c r="CS55" t="inlineStr">
         <is>
@@ -54696,7 +54904,7 @@
       </c>
       <c r="AV56" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW56" t="inlineStr">
@@ -54711,7 +54919,7 @@
       </c>
       <c r="AY56" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ56" t="inlineStr">
@@ -54721,12 +54929,12 @@
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BC56" t="inlineStr">
@@ -54921,11 +55129,15 @@
           <t>18.96</t>
         </is>
       </c>
-      <c r="CQ56" t="n">
-        <v>19</v>
-      </c>
-      <c r="CR56" t="n">
-        <v>19.58</v>
+      <c r="CQ56" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="CR56" t="inlineStr">
+        <is>
+          <t>19.58</t>
+        </is>
       </c>
       <c r="CS56" t="inlineStr">
         <is>
@@ -55678,7 +55890,7 @@
       </c>
       <c r="AV57" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW57" t="inlineStr">
@@ -55693,7 +55905,7 @@
       </c>
       <c r="AY57" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ57" t="inlineStr">
@@ -55703,12 +55915,12 @@
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB57" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BC57" t="inlineStr">
@@ -55903,11 +56115,15 @@
           <t>18.915</t>
         </is>
       </c>
-      <c r="CQ57" t="n">
-        <v>19.02</v>
-      </c>
-      <c r="CR57" t="n">
-        <v>19.59</v>
+      <c r="CQ57" t="inlineStr">
+        <is>
+          <t>19.02</t>
+        </is>
+      </c>
+      <c r="CR57" t="inlineStr">
+        <is>
+          <t>19.59</t>
+        </is>
       </c>
       <c r="CS57" t="inlineStr">
         <is>
@@ -56660,7 +56876,7 @@
       </c>
       <c r="AV58" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW58" t="inlineStr">
@@ -56675,7 +56891,7 @@
       </c>
       <c r="AY58" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ58" t="inlineStr">
@@ -56685,12 +56901,12 @@
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BC58" t="inlineStr">
@@ -56885,11 +57101,15 @@
           <t>18.885</t>
         </is>
       </c>
-      <c r="CQ58" t="n">
-        <v>19.04</v>
-      </c>
-      <c r="CR58" t="n">
-        <v>19.61</v>
+      <c r="CQ58" t="inlineStr">
+        <is>
+          <t>19.04</t>
+        </is>
+      </c>
+      <c r="CR58" t="inlineStr">
+        <is>
+          <t>19.61</t>
+        </is>
       </c>
       <c r="CS58" t="inlineStr">
         <is>
@@ -57642,7 +57862,7 @@
       </c>
       <c r="AV59" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW59" t="inlineStr">
@@ -57657,7 +57877,7 @@
       </c>
       <c r="AY59" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ59" t="inlineStr">
@@ -57667,12 +57887,12 @@
       </c>
       <c r="BA59" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB59" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BC59" t="inlineStr">
@@ -57867,11 +58087,15 @@
           <t>18.92</t>
         </is>
       </c>
-      <c r="CQ59" t="n">
-        <v>19.08</v>
-      </c>
-      <c r="CR59" t="n">
-        <v>19.64</v>
+      <c r="CQ59" t="inlineStr">
+        <is>
+          <t>19.08</t>
+        </is>
+      </c>
+      <c r="CR59" t="inlineStr">
+        <is>
+          <t>19.64</t>
+        </is>
       </c>
       <c r="CS59" t="inlineStr">
         <is>
@@ -58624,7 +58848,7 @@
       </c>
       <c r="AV60" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW60" t="inlineStr">
@@ -58639,7 +58863,7 @@
       </c>
       <c r="AY60" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ60" t="inlineStr">
@@ -58649,12 +58873,12 @@
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BC60" t="inlineStr">
@@ -58849,11 +59073,15 @@
           <t>18.925</t>
         </is>
       </c>
-      <c r="CQ60" t="n">
-        <v>19.14</v>
-      </c>
-      <c r="CR60" t="n">
-        <v>19.66</v>
+      <c r="CQ60" t="inlineStr">
+        <is>
+          <t>19.14</t>
+        </is>
+      </c>
+      <c r="CR60" t="inlineStr">
+        <is>
+          <t>19.66</t>
+        </is>
       </c>
       <c r="CS60" t="inlineStr">
         <is>
@@ -59606,7 +59834,7 @@
       </c>
       <c r="AV61" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW61" t="inlineStr">
@@ -59621,22 +59849,22 @@
       </c>
       <c r="AY61" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB61" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BC61" t="inlineStr">
@@ -59831,11 +60059,15 @@
           <t>18.9</t>
         </is>
       </c>
-      <c r="CQ61" t="n">
-        <v>19.19</v>
-      </c>
-      <c r="CR61" t="n">
-        <v>19.7</v>
+      <c r="CQ61" t="inlineStr">
+        <is>
+          <t>19.19</t>
+        </is>
+      </c>
+      <c r="CR61" t="inlineStr">
+        <is>
+          <t>19.7</t>
+        </is>
       </c>
       <c r="CS61" t="inlineStr">
         <is>
@@ -60588,7 +60820,7 @@
       </c>
       <c r="AV62" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW62" t="inlineStr">
@@ -60603,22 +60835,22 @@
       </c>
       <c r="AY62" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB62" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BC62" t="inlineStr">
@@ -60813,11 +61045,15 @@
           <t>18.87</t>
         </is>
       </c>
-      <c r="CQ62" t="n">
-        <v>19.24</v>
-      </c>
-      <c r="CR62" t="n">
-        <v>19.74</v>
+      <c r="CQ62" t="inlineStr">
+        <is>
+          <t>19.24</t>
+        </is>
+      </c>
+      <c r="CR62" t="inlineStr">
+        <is>
+          <t>19.74</t>
+        </is>
       </c>
       <c r="CS62" t="inlineStr">
         <is>
@@ -61570,7 +61806,7 @@
       </c>
       <c r="AV63" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW63" t="inlineStr">
@@ -61585,22 +61821,22 @@
       </c>
       <c r="AY63" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB63" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BC63" t="inlineStr">
@@ -61795,11 +62031,15 @@
           <t>18.865</t>
         </is>
       </c>
-      <c r="CQ63" t="n">
-        <v>19.29</v>
-      </c>
-      <c r="CR63" t="n">
-        <v>19.78</v>
+      <c r="CQ63" t="inlineStr">
+        <is>
+          <t>19.29</t>
+        </is>
+      </c>
+      <c r="CR63" t="inlineStr">
+        <is>
+          <t>19.78</t>
+        </is>
       </c>
       <c r="CS63" t="inlineStr">
         <is>
@@ -62552,7 +62792,7 @@
       </c>
       <c r="AV64" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW64" t="inlineStr">
@@ -62567,22 +62807,22 @@
       </c>
       <c r="AY64" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB64" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BC64" t="inlineStr">
@@ -62777,11 +63017,15 @@
           <t>18.885</t>
         </is>
       </c>
-      <c r="CQ64" t="n">
-        <v>19.34</v>
-      </c>
-      <c r="CR64" t="n">
-        <v>19.82</v>
+      <c r="CQ64" t="inlineStr">
+        <is>
+          <t>19.34</t>
+        </is>
+      </c>
+      <c r="CR64" t="inlineStr">
+        <is>
+          <t>19.82</t>
+        </is>
       </c>
       <c r="CS64" t="inlineStr">
         <is>
@@ -63529,12 +63773,12 @@
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW65" t="inlineStr">
@@ -63549,22 +63793,22 @@
       </c>
       <c r="AY65" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB65" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BC65" t="inlineStr">
@@ -63759,11 +64003,15 @@
           <t>53.89</t>
         </is>
       </c>
-      <c r="CQ65" t="n">
-        <v>53.36</v>
-      </c>
-      <c r="CR65" t="n">
-        <v>53.06</v>
+      <c r="CQ65" t="inlineStr">
+        <is>
+          <t>53.36</t>
+        </is>
+      </c>
+      <c r="CR65" t="inlineStr">
+        <is>
+          <t>53.06</t>
+        </is>
       </c>
       <c r="CS65" t="inlineStr">
         <is>
@@ -64511,12 +64759,12 @@
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW66" t="inlineStr">
@@ -64526,27 +64774,27 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BB66" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BC66" t="inlineStr">
@@ -64741,11 +64989,15 @@
           <t>53.78000000000001</t>
         </is>
       </c>
-      <c r="CQ66" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="CR66" t="n">
-        <v>53.04</v>
+      <c r="CQ66" t="inlineStr">
+        <is>
+          <t>53.3</t>
+        </is>
+      </c>
+      <c r="CR66" t="inlineStr">
+        <is>
+          <t>53.04</t>
+        </is>
       </c>
       <c r="CS66" t="inlineStr">
         <is>
@@ -65493,12 +65745,12 @@
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AV67" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW67" t="inlineStr">
@@ -65508,27 +65760,27 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BB67" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BC67" t="inlineStr">
@@ -65723,11 +65975,15 @@
           <t>53.61</t>
         </is>
       </c>
-      <c r="CQ67" t="n">
-        <v>53.24</v>
-      </c>
-      <c r="CR67" t="n">
-        <v>53.03</v>
+      <c r="CQ67" t="inlineStr">
+        <is>
+          <t>53.24</t>
+        </is>
+      </c>
+      <c r="CR67" t="inlineStr">
+        <is>
+          <t>53.03</t>
+        </is>
       </c>
       <c r="CS67" t="inlineStr">
         <is>
@@ -66475,42 +66731,42 @@
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BB68" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BC68" t="inlineStr">
@@ -66705,11 +66961,15 @@
           <t>53.45</t>
         </is>
       </c>
-      <c r="CQ68" t="n">
-        <v>53.18</v>
-      </c>
-      <c r="CR68" t="n">
-        <v>53</v>
+      <c r="CQ68" t="inlineStr">
+        <is>
+          <t>53.18</t>
+        </is>
+      </c>
+      <c r="CR68" t="inlineStr">
+        <is>
+          <t>53.0</t>
+        </is>
       </c>
       <c r="CS68" t="inlineStr">
         <is>
@@ -67457,42 +67717,42 @@
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BB69" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BC69" t="inlineStr">
@@ -67687,11 +67947,15 @@
           <t>53.35</t>
         </is>
       </c>
-      <c r="CQ69" t="n">
-        <v>53.16</v>
-      </c>
-      <c r="CR69" t="n">
-        <v>52.96</v>
+      <c r="CQ69" t="inlineStr">
+        <is>
+          <t>53.16</t>
+        </is>
+      </c>
+      <c r="CR69" t="inlineStr">
+        <is>
+          <t>52.96</t>
+        </is>
       </c>
       <c r="CS69" t="inlineStr">
         <is>
@@ -68444,37 +68708,37 @@
       </c>
       <c r="AV70" t="inlineStr">
         <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW70" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AW70" t="inlineStr">
+      <c r="AX70" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
       <c r="AY70" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BB70" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC70" t="inlineStr">
@@ -68669,11 +68933,15 @@
           <t>53.15</t>
         </is>
       </c>
-      <c r="CQ70" t="n">
-        <v>53.11</v>
-      </c>
-      <c r="CR70" t="n">
-        <v>52.92</v>
+      <c r="CQ70" t="inlineStr">
+        <is>
+          <t>53.11</t>
+        </is>
+      </c>
+      <c r="CR70" t="inlineStr">
+        <is>
+          <t>52.92</t>
+        </is>
       </c>
       <c r="CS70" t="inlineStr">
         <is>
@@ -69426,37 +69694,37 @@
       </c>
       <c r="AV71" t="inlineStr">
         <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW71" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AW71" t="inlineStr">
+      <c r="AX71" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="AY71" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BB71" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BC71" t="inlineStr">
@@ -69651,11 +69919,15 @@
           <t>52.97000000000001</t>
         </is>
       </c>
-      <c r="CQ71" t="n">
-        <v>53.04</v>
-      </c>
-      <c r="CR71" t="n">
-        <v>52.88</v>
+      <c r="CQ71" t="inlineStr">
+        <is>
+          <t>53.04</t>
+        </is>
+      </c>
+      <c r="CR71" t="inlineStr">
+        <is>
+          <t>52.88</t>
+        </is>
       </c>
       <c r="CS71" t="inlineStr">
         <is>
@@ -70403,12 +70675,12 @@
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW72" t="inlineStr">
@@ -70423,22 +70695,22 @@
       </c>
       <c r="AY72" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BB72" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC72" t="inlineStr">
@@ -70633,11 +70905,15 @@
           <t>52.82000000000001</t>
         </is>
       </c>
-      <c r="CQ72" t="n">
-        <v>52.97</v>
-      </c>
-      <c r="CR72" t="n">
-        <v>52.84</v>
+      <c r="CQ72" t="inlineStr">
+        <is>
+          <t>52.97</t>
+        </is>
+      </c>
+      <c r="CR72" t="inlineStr">
+        <is>
+          <t>52.84</t>
+        </is>
       </c>
       <c r="CS72" t="inlineStr">
         <is>
@@ -71390,7 +71666,7 @@
       </c>
       <c r="AV73" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW73" t="inlineStr">
@@ -71405,22 +71681,22 @@
       </c>
       <c r="AY73" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BB73" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC73" t="inlineStr">
@@ -71615,11 +71891,15 @@
           <t>52.82000000000001</t>
         </is>
       </c>
-      <c r="CQ73" t="n">
-        <v>52.95</v>
-      </c>
-      <c r="CR73" t="n">
-        <v>52.81</v>
+      <c r="CQ73" t="inlineStr">
+        <is>
+          <t>52.95</t>
+        </is>
+      </c>
+      <c r="CR73" t="inlineStr">
+        <is>
+          <t>52.81</t>
+        </is>
       </c>
       <c r="CS73" t="inlineStr">
         <is>
@@ -72372,7 +72652,7 @@
       </c>
       <c r="AV74" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW74" t="inlineStr">
@@ -72387,22 +72667,22 @@
       </c>
       <c r="AY74" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB74" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BC74" t="inlineStr">
@@ -72597,11 +72877,15 @@
           <t>40.2</t>
         </is>
       </c>
-      <c r="CQ74" t="n">
-        <v>40.17</v>
-      </c>
-      <c r="CR74" t="n">
-        <v>40.05</v>
+      <c r="CQ74" t="inlineStr">
+        <is>
+          <t>40.17</t>
+        </is>
+      </c>
+      <c r="CR74" t="inlineStr">
+        <is>
+          <t>40.05</t>
+        </is>
       </c>
       <c r="CS74" t="inlineStr">
         <is>
@@ -73354,7 +73638,7 @@
       </c>
       <c r="AV75" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW75" t="inlineStr">
@@ -73369,22 +73653,22 @@
       </c>
       <c r="AY75" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB75" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BC75" t="inlineStr">
@@ -73579,11 +73863,15 @@
           <t>40.225</t>
         </is>
       </c>
-      <c r="CQ75" t="n">
-        <v>40.26</v>
-      </c>
-      <c r="CR75" t="n">
-        <v>40.04</v>
+      <c r="CQ75" t="inlineStr">
+        <is>
+          <t>40.26</t>
+        </is>
+      </c>
+      <c r="CR75" t="inlineStr">
+        <is>
+          <t>40.04</t>
+        </is>
       </c>
       <c r="CS75" t="inlineStr">
         <is>
@@ -74336,7 +74624,7 @@
       </c>
       <c r="AV76" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW76" t="inlineStr">
@@ -74351,22 +74639,22 @@
       </c>
       <c r="AY76" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB76" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BC76" t="inlineStr">
@@ -74561,11 +74849,15 @@
           <t>40.22000000000001</t>
         </is>
       </c>
-      <c r="CQ76" t="n">
-        <v>40.29</v>
-      </c>
-      <c r="CR76" t="n">
-        <v>40.01</v>
+      <c r="CQ76" t="inlineStr">
+        <is>
+          <t>40.29</t>
+        </is>
+      </c>
+      <c r="CR76" t="inlineStr">
+        <is>
+          <t>40.01</t>
+        </is>
       </c>
       <c r="CS76" t="inlineStr">
         <is>
@@ -75318,7 +75610,7 @@
       </c>
       <c r="AV77" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW77" t="inlineStr">
@@ -75333,22 +75625,22 @@
       </c>
       <c r="AY77" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB77" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BC77" t="inlineStr">
@@ -75543,11 +75835,15 @@
           <t>40.185</t>
         </is>
       </c>
-      <c r="CQ77" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="CR77" t="n">
-        <v>39.98</v>
+      <c r="CQ77" t="inlineStr">
+        <is>
+          <t>40.3</t>
+        </is>
+      </c>
+      <c r="CR77" t="inlineStr">
+        <is>
+          <t>39.98</t>
+        </is>
       </c>
       <c r="CS77" t="inlineStr">
         <is>
@@ -76300,7 +76596,7 @@
       </c>
       <c r="AV78" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW78" t="inlineStr">
@@ -76315,22 +76611,22 @@
       </c>
       <c r="AY78" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BB78" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BC78" t="inlineStr">
@@ -76525,11 +76821,15 @@
           <t>40.16</t>
         </is>
       </c>
-      <c r="CQ78" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="CR78" t="n">
-        <v>39.96</v>
+      <c r="CQ78" t="inlineStr">
+        <is>
+          <t>40.3</t>
+        </is>
+      </c>
+      <c r="CR78" t="inlineStr">
+        <is>
+          <t>39.96</t>
+        </is>
       </c>
       <c r="CS78" t="inlineStr">
         <is>
@@ -77282,7 +77582,7 @@
       </c>
       <c r="AV79" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW79" t="inlineStr">
@@ -77297,22 +77597,22 @@
       </c>
       <c r="AY79" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BB79" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BC79" t="inlineStr">
@@ -77507,11 +77807,15 @@
           <t>40.185</t>
         </is>
       </c>
-      <c r="CQ79" t="n">
-        <v>40.32</v>
-      </c>
-      <c r="CR79" t="n">
-        <v>39.95</v>
+      <c r="CQ79" t="inlineStr">
+        <is>
+          <t>40.32</t>
+        </is>
+      </c>
+      <c r="CR79" t="inlineStr">
+        <is>
+          <t>39.95</t>
+        </is>
       </c>
       <c r="CS79" t="inlineStr">
         <is>
@@ -78264,7 +78568,7 @@
       </c>
       <c r="AV80" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW80" t="inlineStr">
@@ -78279,22 +78583,22 @@
       </c>
       <c r="AY80" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BB80" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BC80" t="inlineStr">
@@ -78489,11 +78793,15 @@
           <t>40.235</t>
         </is>
       </c>
-      <c r="CQ80" t="n">
-        <v>40.33</v>
-      </c>
-      <c r="CR80" t="n">
-        <v>39.93</v>
+      <c r="CQ80" t="inlineStr">
+        <is>
+          <t>40.33</t>
+        </is>
+      </c>
+      <c r="CR80" t="inlineStr">
+        <is>
+          <t>39.93</t>
+        </is>
       </c>
       <c r="CS80" t="inlineStr">
         <is>
@@ -79241,12 +79549,12 @@
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW81" t="inlineStr">
@@ -79261,22 +79569,22 @@
       </c>
       <c r="AY81" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BB81" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BC81" t="inlineStr">
@@ -79471,11 +79779,15 @@
           <t>40.225</t>
         </is>
       </c>
-      <c r="CQ81" t="n">
-        <v>40.31</v>
-      </c>
-      <c r="CR81" t="n">
-        <v>39.9</v>
+      <c r="CQ81" t="inlineStr">
+        <is>
+          <t>40.31</t>
+        </is>
+      </c>
+      <c r="CR81" t="inlineStr">
+        <is>
+          <t>39.9</t>
+        </is>
       </c>
       <c r="CS81" t="inlineStr">
         <is>
@@ -80228,7 +80540,7 @@
       </c>
       <c r="AV82" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW82" t="inlineStr">
@@ -80243,22 +80555,22 @@
       </c>
       <c r="AY82" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BB82" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BC82" t="inlineStr">
@@ -80453,11 +80765,15 @@
           <t>40.2</t>
         </is>
       </c>
-      <c r="CQ82" t="n">
-        <v>40.29</v>
-      </c>
-      <c r="CR82" t="n">
-        <v>39.87</v>
+      <c r="CQ82" t="inlineStr">
+        <is>
+          <t>40.29</t>
+        </is>
+      </c>
+      <c r="CR82" t="inlineStr">
+        <is>
+          <t>39.87</t>
+        </is>
       </c>
       <c r="CS82" t="inlineStr">
         <is>
@@ -81205,42 +81521,42 @@
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AV83" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BB83" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BC83" t="inlineStr">
@@ -81435,11 +81751,15 @@
           <t>90.87</t>
         </is>
       </c>
-      <c r="CQ83" t="n">
-        <v>86.3</v>
-      </c>
-      <c r="CR83" t="n">
-        <v>78.28</v>
+      <c r="CQ83" t="inlineStr">
+        <is>
+          <t>86.3</t>
+        </is>
+      </c>
+      <c r="CR83" t="inlineStr">
+        <is>
+          <t>78.28</t>
+        </is>
       </c>
       <c r="CS83" t="inlineStr">
         <is>
@@ -81555,7 +81875,7 @@
       </c>
       <c r="DQ83" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR83" t="inlineStr">
@@ -82187,42 +82507,42 @@
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="BB84" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="BC84" t="inlineStr">
@@ -82417,11 +82737,15 @@
           <t>88.92</t>
         </is>
       </c>
-      <c r="CQ84" t="n">
-        <v>85.23999999999999</v>
-      </c>
-      <c r="CR84" t="n">
-        <v>77.98</v>
+      <c r="CQ84" t="inlineStr">
+        <is>
+          <t>85.24</t>
+        </is>
+      </c>
+      <c r="CR84" t="inlineStr">
+        <is>
+          <t>77.98</t>
+        </is>
       </c>
       <c r="CS84" t="inlineStr">
         <is>
@@ -82537,7 +82861,7 @@
       </c>
       <c r="DQ84" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR84" t="inlineStr">
@@ -83169,42 +83493,42 @@
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="BB85" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="BC85" t="inlineStr">
@@ -83399,11 +83723,15 @@
           <t>87.78999999999999</t>
         </is>
       </c>
-      <c r="CQ85" t="n">
-        <v>84.36</v>
-      </c>
-      <c r="CR85" t="n">
-        <v>77.8</v>
+      <c r="CQ85" t="inlineStr">
+        <is>
+          <t>84.36</t>
+        </is>
+      </c>
+      <c r="CR85" t="inlineStr">
+        <is>
+          <t>77.8</t>
+        </is>
       </c>
       <c r="CS85" t="inlineStr">
         <is>
@@ -83519,7 +83847,7 @@
       </c>
       <c r="DQ85" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR85" t="inlineStr">
@@ -84151,42 +84479,42 @@
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BB86" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BC86" t="inlineStr">
@@ -84381,11 +84709,15 @@
           <t>86.34</t>
         </is>
       </c>
-      <c r="CQ86" t="n">
-        <v>83.18000000000001</v>
-      </c>
-      <c r="CR86" t="n">
-        <v>77.41</v>
+      <c r="CQ86" t="inlineStr">
+        <is>
+          <t>83.18</t>
+        </is>
+      </c>
+      <c r="CR86" t="inlineStr">
+        <is>
+          <t>77.41</t>
+        </is>
       </c>
       <c r="CS86" t="inlineStr">
         <is>
@@ -84501,7 +84833,7 @@
       </c>
       <c r="DQ86" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR86" t="inlineStr">
@@ -85133,42 +85465,42 @@
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BB87" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BC87" t="inlineStr">
@@ -85363,11 +85695,15 @@
           <t>85.27</t>
         </is>
       </c>
-      <c r="CQ87" t="n">
-        <v>82.03</v>
-      </c>
-      <c r="CR87" t="n">
-        <v>77.15000000000001</v>
+      <c r="CQ87" t="inlineStr">
+        <is>
+          <t>82.03</t>
+        </is>
+      </c>
+      <c r="CR87" t="inlineStr">
+        <is>
+          <t>77.15</t>
+        </is>
       </c>
       <c r="CS87" t="inlineStr">
         <is>
@@ -85483,7 +85819,7 @@
       </c>
       <c r="DQ87" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR87" t="inlineStr">
@@ -86115,42 +86451,42 @@
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BB88" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BC88" t="inlineStr">
@@ -86345,11 +86681,15 @@
           <t>85.17</t>
         </is>
       </c>
-      <c r="CQ88" t="n">
-        <v>81.3</v>
-      </c>
-      <c r="CR88" t="n">
-        <v>77.01000000000001</v>
+      <c r="CQ88" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="CR88" t="inlineStr">
+        <is>
+          <t>77.01</t>
+        </is>
       </c>
       <c r="CS88" t="inlineStr">
         <is>
@@ -86465,7 +86805,7 @@
       </c>
       <c r="DQ88" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR88" t="inlineStr">
@@ -87097,42 +87437,42 @@
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BB89" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BC89" t="inlineStr">
@@ -87327,11 +87667,15 @@
           <t>85.19</t>
         </is>
       </c>
-      <c r="CQ89" t="n">
-        <v>80.45999999999999</v>
-      </c>
-      <c r="CR89" t="n">
-        <v>76.72</v>
+      <c r="CQ89" t="inlineStr">
+        <is>
+          <t>80.46</t>
+        </is>
+      </c>
+      <c r="CR89" t="inlineStr">
+        <is>
+          <t>76.72</t>
+        </is>
       </c>
       <c r="CS89" t="inlineStr">
         <is>
@@ -87447,7 +87791,7 @@
       </c>
       <c r="DQ89" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR89" t="inlineStr">
@@ -88079,42 +88423,42 @@
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BB90" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC90" t="inlineStr">
@@ -88309,11 +88653,15 @@
           <t>84.43</t>
         </is>
       </c>
-      <c r="CQ90" t="n">
-        <v>79.65000000000001</v>
-      </c>
-      <c r="CR90" t="n">
-        <v>76.3</v>
+      <c r="CQ90" t="inlineStr">
+        <is>
+          <t>79.65</t>
+        </is>
+      </c>
+      <c r="CR90" t="inlineStr">
+        <is>
+          <t>76.3</t>
+        </is>
       </c>
       <c r="CS90" t="inlineStr">
         <is>
@@ -88429,7 +88777,7 @@
       </c>
       <c r="DQ90" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR90" t="inlineStr">
@@ -89061,42 +89409,42 @@
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BB91" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC91" t="inlineStr">
@@ -89291,11 +89639,15 @@
           <t>83.55</t>
         </is>
       </c>
-      <c r="CQ91" t="n">
-        <v>78.72</v>
-      </c>
-      <c r="CR91" t="n">
-        <v>75.79000000000001</v>
+      <c r="CQ91" t="inlineStr">
+        <is>
+          <t>78.72</t>
+        </is>
+      </c>
+      <c r="CR91" t="inlineStr">
+        <is>
+          <t>75.79</t>
+        </is>
       </c>
       <c r="CS91" t="inlineStr">
         <is>
@@ -89411,7 +89763,7 @@
       </c>
       <c r="DQ91" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR91" t="inlineStr">
@@ -90048,7 +90400,7 @@
       </c>
       <c r="AV92" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW92" t="inlineStr">
@@ -90063,22 +90415,22 @@
       </c>
       <c r="AY92" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB92" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BC92" t="inlineStr">
@@ -90273,11 +90625,15 @@
           <t>13.27</t>
         </is>
       </c>
-      <c r="CQ92" t="n">
-        <v>13.31</v>
-      </c>
-      <c r="CR92" t="n">
-        <v>13.4</v>
+      <c r="CQ92" t="inlineStr">
+        <is>
+          <t>13.31</t>
+        </is>
+      </c>
+      <c r="CR92" t="inlineStr">
+        <is>
+          <t>13.4</t>
+        </is>
       </c>
       <c r="CS92" t="inlineStr">
         <is>
@@ -91030,7 +91386,7 @@
       </c>
       <c r="AV93" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW93" t="inlineStr">
@@ -91045,22 +91401,22 @@
       </c>
       <c r="AY93" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB93" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BC93" t="inlineStr">
@@ -91255,11 +91611,15 @@
           <t>13.275</t>
         </is>
       </c>
-      <c r="CQ93" t="n">
-        <v>13.32</v>
-      </c>
-      <c r="CR93" t="n">
-        <v>13.41</v>
+      <c r="CQ93" t="inlineStr">
+        <is>
+          <t>13.32</t>
+        </is>
+      </c>
+      <c r="CR93" t="inlineStr">
+        <is>
+          <t>13.41</t>
+        </is>
       </c>
       <c r="CS93" t="inlineStr">
         <is>
@@ -92012,7 +92372,7 @@
       </c>
       <c r="AV94" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW94" t="inlineStr">
@@ -92027,22 +92387,22 @@
       </c>
       <c r="AY94" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB94" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BC94" t="inlineStr">
@@ -92237,11 +92597,15 @@
           <t>13.27</t>
         </is>
       </c>
-      <c r="CQ94" t="n">
-        <v>13.33</v>
-      </c>
-      <c r="CR94" t="n">
-        <v>13.42</v>
+      <c r="CQ94" t="inlineStr">
+        <is>
+          <t>13.33</t>
+        </is>
+      </c>
+      <c r="CR94" t="inlineStr">
+        <is>
+          <t>13.42</t>
+        </is>
       </c>
       <c r="CS94" t="inlineStr">
         <is>
@@ -92994,7 +93358,7 @@
       </c>
       <c r="AV95" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW95" t="inlineStr">
@@ -93009,22 +93373,22 @@
       </c>
       <c r="AY95" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB95" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BC95" t="inlineStr">
@@ -93219,11 +93583,15 @@
           <t>13.27</t>
         </is>
       </c>
-      <c r="CQ95" t="n">
-        <v>13.34</v>
-      </c>
-      <c r="CR95" t="n">
-        <v>13.42</v>
+      <c r="CQ95" t="inlineStr">
+        <is>
+          <t>13.34</t>
+        </is>
+      </c>
+      <c r="CR95" t="inlineStr">
+        <is>
+          <t>13.42</t>
+        </is>
       </c>
       <c r="CS95" t="inlineStr">
         <is>
@@ -93976,7 +94344,7 @@
       </c>
       <c r="AV96" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW96" t="inlineStr">
@@ -93991,22 +94359,22 @@
       </c>
       <c r="AY96" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB96" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BC96" t="inlineStr">
@@ -94201,11 +94569,15 @@
           <t>13.285</t>
         </is>
       </c>
-      <c r="CQ96" t="n">
-        <v>13.34</v>
-      </c>
-      <c r="CR96" t="n">
-        <v>13.43</v>
+      <c r="CQ96" t="inlineStr">
+        <is>
+          <t>13.34</t>
+        </is>
+      </c>
+      <c r="CR96" t="inlineStr">
+        <is>
+          <t>13.43</t>
+        </is>
       </c>
       <c r="CS96" t="inlineStr">
         <is>
@@ -94958,7 +95330,7 @@
       </c>
       <c r="AV97" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW97" t="inlineStr">
@@ -94973,22 +95345,22 @@
       </c>
       <c r="AY97" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB97" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BC97" t="inlineStr">
@@ -95183,11 +95555,15 @@
           <t>13.295</t>
         </is>
       </c>
-      <c r="CQ97" t="n">
-        <v>13.36</v>
-      </c>
-      <c r="CR97" t="n">
-        <v>13.44</v>
+      <c r="CQ97" t="inlineStr">
+        <is>
+          <t>13.36</t>
+        </is>
+      </c>
+      <c r="CR97" t="inlineStr">
+        <is>
+          <t>13.44</t>
+        </is>
       </c>
       <c r="CS97" t="inlineStr">
         <is>
@@ -95940,7 +96316,7 @@
       </c>
       <c r="AV98" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW98" t="inlineStr">
@@ -95955,22 +96331,22 @@
       </c>
       <c r="AY98" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB98" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BC98" t="inlineStr">
@@ -96165,11 +96541,15 @@
           <t>13.305</t>
         </is>
       </c>
-      <c r="CQ98" t="n">
-        <v>13.37</v>
-      </c>
-      <c r="CR98" t="n">
-        <v>13.45</v>
+      <c r="CQ98" t="inlineStr">
+        <is>
+          <t>13.37</t>
+        </is>
+      </c>
+      <c r="CR98" t="inlineStr">
+        <is>
+          <t>13.45</t>
+        </is>
       </c>
       <c r="CS98" t="inlineStr">
         <is>
@@ -96922,7 +97302,7 @@
       </c>
       <c r="AV99" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW99" t="inlineStr">
@@ -96937,22 +97317,22 @@
       </c>
       <c r="AY99" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB99" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BC99" t="inlineStr">
@@ -97147,11 +97527,15 @@
           <t>13.305</t>
         </is>
       </c>
-      <c r="CQ99" t="n">
-        <v>13.37</v>
-      </c>
-      <c r="CR99" t="n">
-        <v>13.45</v>
+      <c r="CQ99" t="inlineStr">
+        <is>
+          <t>13.37</t>
+        </is>
+      </c>
+      <c r="CR99" t="inlineStr">
+        <is>
+          <t>13.45</t>
+        </is>
       </c>
       <c r="CS99" t="inlineStr">
         <is>
@@ -97904,7 +98288,7 @@
       </c>
       <c r="AV100" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW100" t="inlineStr">
@@ -97919,22 +98303,22 @@
       </c>
       <c r="AY100" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB100" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BC100" t="inlineStr">
@@ -98129,11 +98513,15 @@
           <t>13.315</t>
         </is>
       </c>
-      <c r="CQ100" t="n">
-        <v>13.38</v>
-      </c>
-      <c r="CR100" t="n">
-        <v>13.46</v>
+      <c r="CQ100" t="inlineStr">
+        <is>
+          <t>13.38</t>
+        </is>
+      </c>
+      <c r="CR100" t="inlineStr">
+        <is>
+          <t>13.46</t>
+        </is>
       </c>
       <c r="CS100" t="inlineStr">
         <is>
